--- a/Assessment Questions/CDE/DATA ENGINEERING ASSOCIATE/DATA ORCHESTRATION WITH APACHE AIRFLOW/Executing Airflow/airflow_execution_questions.xlsx
+++ b/Assessment Questions/CDE/DATA ENGINEERING ASSOCIATE/DATA ORCHESTRATION WITH APACHE AIRFLOW/Executing Airflow/airflow_execution_questions.xlsx
@@ -7,7 +7,7 @@
     <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Airflow Execution" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="questions" sheetId="1" state="visible" r:id="rId1"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -434,12 +434,12 @@
       </c>
       <c r="D1" t="inlineStr">
         <is>
-          <t>Correct Answer</t>
+          <t>Explanation</t>
         </is>
       </c>
       <c r="E1" t="inlineStr">
         <is>
-          <t>Explanation</t>
+          <t>Question Type</t>
         </is>
       </c>
     </row>
@@ -454,15 +454,14 @@
           <t>One-word</t>
         </is>
       </c>
-      <c r="C2" t="inlineStr"/>
       <c r="D2" t="inlineStr">
         <is>
-          <t>airflow dags trigger</t>
+          <t>Use this command to manually start a DAG run.</t>
         </is>
       </c>
       <c r="E2" t="inlineStr">
         <is>
-          <t>Use this command to manually start a DAG run.</t>
+          <t>Short Answer</t>
         </is>
       </c>
     </row>
@@ -477,15 +476,14 @@
           <t>One-word</t>
         </is>
       </c>
-      <c r="C3" t="inlineStr"/>
       <c r="D3" t="inlineStr">
         <is>
-          <t>airflow dags list</t>
+          <t>This shows all available DAGs.</t>
         </is>
       </c>
       <c r="E3" t="inlineStr">
         <is>
-          <t>This shows all available DAGs.</t>
+          <t>Short Answer</t>
         </is>
       </c>
     </row>
@@ -500,15 +498,14 @@
           <t>One-word</t>
         </is>
       </c>
-      <c r="C4" t="inlineStr"/>
       <c r="D4" t="inlineStr">
         <is>
-          <t>airflow tasks list</t>
+          <t>This lists all tasks in a DAG.</t>
         </is>
       </c>
       <c r="E4" t="inlineStr">
         <is>
-          <t>This lists all tasks in a DAG.</t>
+          <t>Short Answer</t>
         </is>
       </c>
     </row>
@@ -523,15 +520,14 @@
           <t>One-word</t>
         </is>
       </c>
-      <c r="C5" t="inlineStr"/>
       <c r="D5" t="inlineStr">
         <is>
-          <t>airflow tasks clear</t>
+          <t>Clears task states allowing re-execution.</t>
         </is>
       </c>
       <c r="E5" t="inlineStr">
         <is>
-          <t>Clears task states allowing re-execution.</t>
+          <t>Short Answer</t>
         </is>
       </c>
     </row>
@@ -546,15 +542,14 @@
           <t>One-word</t>
         </is>
       </c>
-      <c r="C6" t="inlineStr"/>
       <c r="D6" t="inlineStr">
         <is>
-          <t>Historical runs</t>
+          <t>airflow dags backfill runs DAG for past dates.</t>
         </is>
       </c>
       <c r="E6" t="inlineStr">
         <is>
-          <t>airflow dags backfill runs DAG for past dates.</t>
+          <t>Short Answer</t>
         </is>
       </c>
     </row>
@@ -569,15 +564,14 @@
           <t>One-word</t>
         </is>
       </c>
-      <c r="C7" t="inlineStr"/>
       <c r="D7" t="inlineStr">
         <is>
-          <t>airflow tasks mark-success</t>
+          <t>This manually sets a task state to success.</t>
         </is>
       </c>
       <c r="E7" t="inlineStr">
         <is>
-          <t>This manually sets a task state to success.</t>
+          <t>Short Answer</t>
         </is>
       </c>
     </row>
@@ -592,15 +586,14 @@
           <t>One-word</t>
         </is>
       </c>
-      <c r="C8" t="inlineStr"/>
       <c r="D8" t="inlineStr">
         <is>
-          <t>airflow dags unpause</t>
+          <t>This enables scheduling for a DAG.</t>
         </is>
       </c>
       <c r="E8" t="inlineStr">
         <is>
-          <t>This enables scheduling for a DAG.</t>
+          <t>Short Answer</t>
         </is>
       </c>
     </row>
@@ -615,15 +608,14 @@
           <t>One-word</t>
         </is>
       </c>
-      <c r="C9" t="inlineStr"/>
       <c r="D9" t="inlineStr">
         <is>
-          <t>airflow tasks logs</t>
+          <t>This displays task execution logs.</t>
         </is>
       </c>
       <c r="E9" t="inlineStr">
         <is>
-          <t>This displays task execution logs.</t>
+          <t>Short Answer</t>
         </is>
       </c>
     </row>
@@ -638,15 +630,14 @@
           <t>One-word</t>
         </is>
       </c>
-      <c r="C10" t="inlineStr"/>
       <c r="D10" t="inlineStr">
         <is>
-          <t>Execution identifier</t>
+          <t>Run ID uniquely identifies a DAG run.</t>
         </is>
       </c>
       <c r="E10" t="inlineStr">
         <is>
-          <t>Run ID uniquely identifies a DAG run.</t>
+          <t>Short Answer</t>
         </is>
       </c>
     </row>
@@ -668,12 +659,12 @@
       </c>
       <c r="D11" t="inlineStr">
         <is>
-          <t>A</t>
+          <t>Clearing a single task retries just that task.</t>
         </is>
       </c>
       <c r="E11" t="inlineStr">
         <is>
-          <t>Clearing a single task retries just that task.</t>
+          <t>Scenario-Based</t>
         </is>
       </c>
     </row>
@@ -688,15 +679,14 @@
           <t>One-word</t>
         </is>
       </c>
-      <c r="C12" t="inlineStr"/>
       <c r="D12" t="inlineStr">
         <is>
-          <t>Configuration</t>
+          <t>Passes configuration JSON to the DAG run.</t>
         </is>
       </c>
       <c r="E12" t="inlineStr">
         <is>
-          <t>Passes configuration JSON to the DAG run.</t>
+          <t>Short Answer</t>
         </is>
       </c>
     </row>
@@ -711,15 +701,14 @@
           <t>One-word</t>
         </is>
       </c>
-      <c r="C13" t="inlineStr"/>
       <c r="D13" t="inlineStr">
         <is>
-          <t>airflow tasks test</t>
+          <t>Use test command to run a task locally.</t>
         </is>
       </c>
       <c r="E13" t="inlineStr">
         <is>
-          <t>Use test command to run a task locally.</t>
+          <t>Short Answer</t>
         </is>
       </c>
     </row>
@@ -734,15 +723,14 @@
           <t>One-word</t>
         </is>
       </c>
-      <c r="C14" t="inlineStr"/>
       <c r="D14" t="inlineStr">
         <is>
-          <t>Database vs no DB</t>
+          <t>Test doesn't record state; run does.</t>
         </is>
       </c>
       <c r="E14" t="inlineStr">
         <is>
-          <t>Test doesn't record state; run does.</t>
+          <t>Short Answer</t>
         </is>
       </c>
     </row>
@@ -757,15 +745,14 @@
           <t>One-word</t>
         </is>
       </c>
-      <c r="C15" t="inlineStr"/>
       <c r="D15" t="inlineStr">
         <is>
-          <t>airflow scheduler status</t>
+          <t>This shows if the scheduler is running.</t>
         </is>
       </c>
       <c r="E15" t="inlineStr">
         <is>
-          <t>This shows if the scheduler is running.</t>
+          <t>Short Answer</t>
         </is>
       </c>
     </row>
@@ -780,15 +767,14 @@
           <t>One-word</t>
         </is>
       </c>
-      <c r="C16" t="inlineStr"/>
       <c r="D16" t="inlineStr">
         <is>
-          <t>airflow dags show</t>
+          <t>This generates a PNG of the DAG structure.</t>
         </is>
       </c>
       <c r="E16" t="inlineStr">
         <is>
-          <t>This generates a PNG of the DAG structure.</t>
+          <t>Short Answer</t>
         </is>
       </c>
     </row>
@@ -803,15 +789,14 @@
           <t>One-word</t>
         </is>
       </c>
-      <c r="C17" t="inlineStr"/>
       <c r="D17" t="inlineStr">
         <is>
-          <t>airflow dags list-runs</t>
+          <t>This shows current and recent DAG runs.</t>
         </is>
       </c>
       <c r="E17" t="inlineStr">
         <is>
-          <t>This shows current and recent DAG runs.</t>
+          <t>Short Answer</t>
         </is>
       </c>
     </row>
@@ -826,15 +811,14 @@
           <t>One-word</t>
         </is>
       </c>
-      <c r="C18" t="inlineStr"/>
       <c r="D18" t="inlineStr">
         <is>
-          <t>airflow standalone</t>
+          <t>Standalone mode runs all services in one process.</t>
         </is>
       </c>
       <c r="E18" t="inlineStr">
         <is>
-          <t>Standalone mode runs all services in one process.</t>
+          <t>Short Answer</t>
         </is>
       </c>
     </row>
@@ -856,12 +840,12 @@
       </c>
       <c r="D19" t="inlineStr">
         <is>
-          <t>A</t>
+          <t>Checking DAG run status helps identify the issue.</t>
         </is>
       </c>
       <c r="E19" t="inlineStr">
         <is>
-          <t>Checking DAG run status helps identify the issue.</t>
+          <t>Scenario-Based</t>
         </is>
       </c>
     </row>
@@ -876,15 +860,14 @@
           <t>One-word</t>
         </is>
       </c>
-      <c r="C20" t="inlineStr"/>
       <c r="D20" t="inlineStr">
         <is>
-          <t>airflow dags pause</t>
+          <t>This stops scheduling of the DAG.</t>
         </is>
       </c>
       <c r="E20" t="inlineStr">
         <is>
-          <t>This stops scheduling of the DAG.</t>
+          <t>Short Answer</t>
         </is>
       </c>
     </row>
@@ -899,15 +882,14 @@
           <t>One-word</t>
         </is>
       </c>
-      <c r="C21" t="inlineStr"/>
       <c r="D21" t="inlineStr">
         <is>
-          <t>airflow dags list-import-errors</t>
+          <t>This shows import errors in DAG files.</t>
         </is>
       </c>
       <c r="E21" t="inlineStr">
         <is>
-          <t>This shows import errors in DAG files.</t>
+          <t>Short Answer</t>
         </is>
       </c>
     </row>
